--- a/spreadsheet/tread_inspections_template.xlsx
+++ b/spreadsheet/tread_inspections_template.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Thresholds" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inspections'!$A$1:$Y$2000</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inspections'!$A$1:$AK$2000</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -592,6 +592,18 @@
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="34" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="6" customWidth="1" min="32" max="32"/>
+    <col width="9" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="8" customWidth="1" min="35" max="35"/>
+    <col width="8" customWidth="1" min="36" max="36"/>
+    <col width="9" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -720,6 +732,66 @@
           <t>scan_confidence_32nds</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>survey_id</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>reported_by</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>vehicle_type</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>axle_role</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>config_code</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>valve_cap</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pull_point_32nds</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>rec_psi</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>min_psi</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>retreads_allowed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -825,9 +897,61 @@
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>165881</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>Clarington, Ontario</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>M. Francis</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>Tractor - Class 8</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>steer</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>2S-4D-4D</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y2000"/>
+  <autoFilter ref="A1:AK2000"/>
   <conditionalFormatting sqref="U2:U2000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"REPLACE"</formula>
@@ -2869,7 +2993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -3048,6 +3172,13 @@
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Formulas cover Inspections rows 2 to 2000. If you exceed that, widen the ranges on Fleet Summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Columns Z onward feed the yard check report (tools/yardcheck): survey, vehicle type, axle role, config code, slot, valve cap and the fleet policy that applied.</t>
         </is>
       </c>
     </row>
